--- a/Business_Budget_Planner.xlsx
+++ b/Business_Budget_Planner.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Monthly Budget" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Budget" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,18 +20,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
-  <si>
-    <t xml:space="preserve">MONTHLY BUDGET PLANNER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Track your income and expenses. Blue cells are for you to fill in.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Month:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Enter Month]</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+  <si>
+    <t xml:space="preserve">BUSINESS BUDGET &amp; CASH FLOW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan your income and expenses with confidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUSINESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Your Business Name]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERIOD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Month / Year]</t>
   </si>
   <si>
     <t xml:space="preserve">  INCOME</t>
@@ -43,19 +49,16 @@
     <t xml:space="preserve">Amount (R)</t>
   </si>
   <si>
-    <t xml:space="preserve">Salary / Wages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business Income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Side Hustle</t>
+    <t xml:space="preserve">Sales Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Income</t>
   </si>
   <si>
     <t xml:space="preserve">Other Income</t>
   </si>
   <si>
-    <t xml:space="preserve">[Add income source]</t>
+    <t xml:space="preserve">[Add source]</t>
   </si>
   <si>
     <t xml:space="preserve">  TOTAL INCOME</t>
@@ -73,22 +76,22 @@
     <t xml:space="preserve">Actual (R)</t>
   </si>
   <si>
-    <t xml:space="preserve">Rent / Bond</t>
+    <t xml:space="preserve">Rent / Premises</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salaries &amp; Wages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stock / Materials</t>
   </si>
   <si>
     <t xml:space="preserve">Electricity &amp; Water</t>
   </si>
   <si>
-    <t xml:space="preserve">Groceries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transport / Petrol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airtime &amp; Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">School Fees</t>
+    <t xml:space="preserve">Transport / Fuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing</t>
   </si>
   <si>
     <t xml:space="preserve">Insurance</t>
@@ -97,12 +100,6 @@
     <t xml:space="preserve">Loan Repayments</t>
   </si>
   <si>
-    <t xml:space="preserve">Savings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entertainment</t>
-  </si>
-  <si>
     <t xml:space="preserve">Other</t>
   </si>
   <si>
@@ -112,10 +109,10 @@
     <t xml:space="preserve">  TOTAL EXPENSES</t>
   </si>
   <si>
-    <t xml:space="preserve">  MONEY LEFT (Income - Expenses)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tip: If Money Left is negative (red), reduce expenses or increase income.</t>
+    <t xml:space="preserve">  NET CASH FLOW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive = profit. Negative = review your expenses.</t>
   </si>
 </sst>
 </file>
@@ -127,7 +124,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
     <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -152,69 +149,55 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="20"/>
-      <color rgb="FF2563EB"/>
-      <name val="Arial"/>
+      <sz val="18"/>
+      <color rgb="FF0F172A"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
+      <i val="true"/>
       <sz val="10"/>
-      <color rgb="FF64748B"/>
-      <name val="Arial"/>
+      <color rgb="FF94A3B8"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF1E293B"/>
-      <name val="Arial"/>
+      <sz val="8"/>
+      <color rgb="FF94A3B8"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF2563EB"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <sz val="10"/>
+      <color rgb="FF0F172A"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF1E293B"/>
-      <name val="Arial"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF475569"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <color rgb="FF94A3B8"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -222,24 +205,37 @@
       <b val="true"/>
       <sz val="13"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF64748B"/>
-      <name val="Arial"/>
+      <i val="true"/>
+      <sz val="8"/>
+      <color rgb="FF94A3B8"/>
+      <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2563EB"/>
+        <bgColor rgb="FF0066CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF059669"/>
+        <bgColor rgb="FF008080"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -249,8 +245,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF16A34A"/>
-        <bgColor rgb="FF008080"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFF1F5F9"/>
       </patternFill>
     </fill>
     <fill>
@@ -261,8 +257,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E293B"/>
-        <bgColor rgb="FF003366"/>
+        <fgColor rgb="FF0F172A"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -276,16 +272,16 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
-        <color rgb="FFCBD5E1"/>
+        <color rgb="FFE2E8F0"/>
       </left>
       <right style="thin">
-        <color rgb="FFCBD5E1"/>
+        <color rgb="FFE2E8F0"/>
       </right>
       <top style="thin">
-        <color rgb="FFCBD5E1"/>
+        <color rgb="FFE2E8F0"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFCBD5E1"/>
+        <color rgb="FFE2E8F0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -315,11 +311,15 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -332,7 +332,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -340,55 +340,83 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -416,17 +444,17 @@
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF059669"/>
       <rgbColor rgb="FFC0C0C0"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFF1F5F9"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFE2E8F0"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCBD5E1"/>
+      <rgbColor rgb="FFCCCCFF"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -449,16 +477,16 @@
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF64748B"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF475569"/>
+      <rgbColor rgb="FF94A3B8"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF16A34A"/>
-      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF0F172A"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF1E293B"/>
+      <rgbColor rgb="FF333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -644,236 +672,233 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:E35"/>
+  <dimension ref="B1:D34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="2.5"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+    <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="2" t="s">
         <v>0</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2" t="s">
-        <v>1</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="7" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="8" t="s">
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="9"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
+      <c r="C10" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="9"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="9"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="9"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="9"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="9"/>
+      <c r="B14" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" s="9"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="12" t="n">
-        <f aca="false">SUM(C9:C14)</f>
+      <c r="C15" s="11"/>
+      <c r="D15" s="12"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="18" t="n">
+        <f aca="false">SUM(C11:C15)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="6" t="s">
+      <c r="D16" s="19"/>
+    </row>
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="8" t="s">
+      <c r="D19" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="14" t="s">
+      <c r="C30" s="22" t="n">
+        <f aca="false">SUM(C20:C29)</f>
+        <v>0</v>
+      </c>
+      <c r="D30" s="22" t="n">
+        <f aca="false">SUM(D20:D29)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="15" t="n">
-        <f aca="false">SUM(C19:C30)</f>
+      <c r="C32" s="24" t="n">
+        <f aca="false">C16-D30</f>
         <v>0</v>
       </c>
-      <c r="D31" s="15" t="n">
-        <f aca="false">SUM(D19:D30)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="16" t="s">
+      <c r="D32" s="25"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="26" t="s">
         <v>30</v>
-      </c>
-      <c r="C33" s="17" t="n">
-        <f aca="false">C15-D31</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="18" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B18:D18"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
